--- a/Puzzles/Puzzles.xlsx
+++ b/Puzzles/Puzzles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\System Folders\Documents\Programming\Projects\Mahjong-wwyd\Puzzles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0139356C-AD22-427F-8A70-5033ECE19FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3420088-F434-4100-A8E8-C2BEDFF3B5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{6FE3E451-891F-4A80-82DE-8D0CC13A8F1E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6FE3E451-891F-4A80-82DE-8D0CC13A8F1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="126">
   <si>
     <t>ID</t>
   </si>
@@ -132,19 +132,10 @@
     <t>Q-Num</t>
   </si>
   <si>
-    <t>678889m 40578p 33s</t>
-  </si>
-  <si>
     <t>1s</t>
   </si>
   <si>
-    <t>678889m 40578p 11z</t>
-  </si>
-  <si>
     <t>2m</t>
-  </si>
-  <si>
-    <t>33m 223677888p 45s</t>
   </si>
   <si>
     <t>6s</t>
@@ -180,9 +171,6 @@
     <t>7m</t>
   </si>
   <si>
-    <t>112m 223677888p 5s</t>
-  </si>
-  <si>
     <t>4s</t>
   </si>
   <si>
@@ -195,28 +183,10 @@
     <t>2m43 8p43 3p39 6p38 1m36 2p36</t>
   </si>
   <si>
-    <t>Take out the completed shape 567p. You can see the sanmenchan with a 7p attached. Fixing the head in souzu is great both for value and acceptance. See: 67m 345677p 334s + 567p</t>
-  </si>
-  <si>
     <t>The acceptance varies greatly depending on the presence of 2 heads. 3s is out because the loss in tile acceptance is too big. It becomes a choice between 5p and 4s, fixing the head on souzu or pinzu. 5p acceptance is better and you'll probably get Tanyao anyway. If you need points, it's okay to cut 2p and confirm Tanyao.</t>
   </si>
   <si>
     <t>Dora 3 2-shanten hand. Keep 3 heads so you can move to 2 at 1-shanten. You can also move towards Tanyao. Cutting 8p isn't too bad (and probably easier to spot), but it's better not to touch the complex shape in pinzu until later.</t>
-  </si>
-  <si>
-    <t>302 "Established Practice" Which to cut? (wwyd-chan 2)</t>
-  </si>
-  <si>
-    <t>303 "Established Practice" Which to cut? (wwyd-chan 2)</t>
-  </si>
-  <si>
-    <t>304 "Established Practice" Which to cut? (wwyd-chan 2)</t>
-  </si>
-  <si>
-    <t>305 "Established Practice" Which to cut? (wwyd-chan 2)</t>
-  </si>
-  <si>
-    <t>306 "Established Practice" Which to cut? (wwyd-chan 2)</t>
   </si>
   <si>
     <t>4z</t>
@@ -237,9 +207,6 @@
     <t>5m</t>
   </si>
   <si>
-    <t>223067m 557p 2234s</t>
-  </si>
-  <si>
     <t>223055677p 2345s</t>
   </si>
   <si>
@@ -249,16 +216,7 @@
     <t>5m22 1p20 6m16 3p16</t>
   </si>
   <si>
-    <t>Don't cut the 1p to aim for Tanyao. Because you have 3 heads, you should cut one of them. This way you can increase your tile acceptance. It is easy to visualize the 3 heads if you think as following: 556m 133p 22s + 345678p</t>
-  </si>
-  <si>
-    <t>While this can be hard at a first look, try to isolate 567p: 223057p 23456s + 567p. It the same shape as previous question, just replacing manzu with pinzu. It is easily solved if you take out the completed shapes.</t>
-  </si>
-  <si>
     <t>7z</t>
-  </si>
-  <si>
-    <t>3p19 3s18 1p13 4p13 2s12</t>
   </si>
   <si>
     <t>Because you have 3 heads, it's fine to fix the ryanmen. Between 3p and 3s pairs, one 3p is already used in the 123p shape. Fix that ryanmen to get 1 more tile to wait on. Even if it's just 1 tile to draw, consider calls: pon is 4 times faster than tsumo, so you can't underestimate it.</t>
@@ -285,25 +243,178 @@
     <t>66m 233345p 22388s</t>
   </si>
   <si>
-    <t>2s22 3p19 2p17 3p16 5p13</t>
+    <t>778m 222344p 3067s</t>
   </si>
   <si>
-    <t>307 "Established Practice" Which to cut? (wwyd-chan 2)</t>
+    <t>4p23 8m20 3p20 7m16 2p11</t>
   </si>
   <si>
-    <t>308 "Established Practice" Which to cut? (wwyd-chan 2)</t>
+    <t>If you drop 8m, you'll have a Iipeikou chance, but you'll need 3p to win the hand. Look at the future, and drop 4p to get the best tile acceptance. You'll get a sure ryanmen tenpai wait.</t>
   </si>
   <si>
-    <t>309 "Established Practice" Which to cut? (wwyd-chan 2)</t>
+    <t>3s</t>
   </si>
   <si>
-    <t>310 "Established Practice" Which to cut? (wwyd-chan 2)</t>
+    <t>7m20 4p17 2p15 8m14 3p14</t>
   </si>
   <si>
-    <t>311 "Established Practice" Which to cut? (wwyd-chan 2)</t>
+    <t>The correct answer is 7m, which gives the highest tile acceptance. You have a 50% chance to get Tanyao, but have the potential of Mentanpin Iipeikou Aka. 8m and 4p reduce your win rate by being slower. Don't forget that modern mahjong is about making good-shape closed hand and call Riichi. In all last agari toppu, you can discard 8m or 4p and call everything, but this is not the right play in early East 1.</t>
   </si>
   <si>
-    <t>312 "Established Practice" Which to cut? (wwyd-chan 2)</t>
+    <t>345m 233444p 0667s</t>
+  </si>
+  <si>
+    <t>4m</t>
+  </si>
+  <si>
+    <t>3p37 2p34 4m30 6s30 4p11</t>
+  </si>
+  <si>
+    <t>The bulging shapes always produces ryanmen, so the theory says to fix the head. Between 2p and 3p, the correct answer is p3 to get Pinfu.</t>
+  </si>
+  <si>
+    <t>345688m 0667p 456s</t>
+  </si>
+  <si>
+    <t>6p46 6s42 3m38 6m38 8m12</t>
+  </si>
+  <si>
+    <t>You should see 8m as the head. You're left with 3456m nobetan, 0667p bulging and 4566s aryanmen. The first 2 can accept 4 kinds of tiles, while the latter can accept only 2. Cut the aryanment by dropping 6s. *When in doubt discard aryanmen. It's usually the correct answer.*</t>
+  </si>
+  <si>
+    <t>3445m 335678p 567s</t>
+  </si>
+  <si>
+    <t>4m46 5p42 8p42 5s38 8s38 3p12</t>
+  </si>
+  <si>
+    <t>You want to keep the manzu shape for Tanyao. The question is from where to cut, the pinzu or the souzu. It is generally better not to mess with the head, so the answer is 8p (you gain 4 tiles). Also the final shape of the hand is better: you can end up with a full sanmenchan (11 tiles), while you'd end up with a worse acceptance on pinzu (2 3p are already used as head). Both the acceptance now and in tenpai are better with the 8p cut.</t>
+  </si>
+  <si>
+    <t>3445m 335678p 234s</t>
+  </si>
+  <si>
+    <t>4m46 5p42 8p42 2s38 5s38 3p12</t>
+  </si>
+  <si>
+    <t>It is easy to miss, but you can see the 345 Sanshoku (If you don't, read Flow book 1 by Sakurai). Keep the bulging shape and foresee the draw of 3p-4p.</t>
+  </si>
+  <si>
+    <t>3405999m 556p 567s</t>
+  </si>
+  <si>
+    <t>6p46 5m41 5s37 8s37 5p20</t>
+  </si>
+  <si>
+    <t>When in doubt, cut aryanmen. The 4 tiles shape in souzu (nobetan) can make a head out of 2 types of tiles (58s), while making ryanmen on 4 (45679s). *556p* this is a shape that can be either a head or sequence.</t>
+  </si>
+  <si>
+    <t>44789m 0678p 4066s</t>
+  </si>
+  <si>
+    <t>0m</t>
+  </si>
+  <si>
+    <t>0m46 6s40 0p36 8p36 4m20</t>
+  </si>
+  <si>
+    <t>In the early turns you'd drop 4m, to utilize all the akadora. As it is already the 7th turn, losing 20 tiles acceptance is too much. Thinking of the final form and the speed, the best choice is 6s, both from winning rate and expected value.</t>
+  </si>
+  <si>
+    <t>3m58 3p51 6p51 3s51 6s51 4m23</t>
+  </si>
+  <si>
+    <t>The best tile to get a fast tenpai is 3m, but if you look at the winrate it becomes inferior to 36p and 36s. You keep the manzu shape and look to cut from either the pinzu or souzu. It is slightly better to keep the pinzu as they don't have the aka 5p. Moreover, you must not forget that there is a possibility of 345 Sanshoku. Even if by a small amount, 6s gives the best expected value. By the way, even without Sanshoku, cutting 3m wouldn't be the best choice.</t>
+  </si>
+  <si>
+    <t>5678m 3456p 78899s</t>
+  </si>
+  <si>
+    <t>8s57 7s54 5m42 8m42 3p38 9s15</t>
+  </si>
+  <si>
+    <t>It's easy to get a Pinfu tenpai. You lose the Iipeikou, but its final shape would need a bad wait 7s. In first place completing it is hard because only 3 tiles are left, and even if you could do it, you'd lose Pinfu. Don't aim for Iipeikou at the edges, unless you really need the han.</t>
+  </si>
+  <si>
+    <t>5678m 1234p 67788s</t>
+  </si>
+  <si>
+    <t>7s49 6s46 1p42 5m38 8m38 8s19</t>
+  </si>
+  <si>
+    <t>The 1234p shape at the edge is functionally a sequence + a floating tile, it is difficult to use. In particular, I don't want to end with a penchan 12p, if I were to draw a 2p.</t>
+  </si>
+  <si>
+    <t>5678m 2345p 56677s</t>
+  </si>
+  <si>
+    <t>8m</t>
+  </si>
+  <si>
+    <t>6s53 5s50 5m42 8m42 2p42 7s19</t>
+  </si>
+  <si>
+    <t>This is a beautiful shape. Don't touch 566777s, as it can become 2 sequences or 1 sequence + 1 head. 58m and 25p are equivalent from both tenpai and win rates, but you can see the 567 Sanshoku (by drawing either 6p or 7p), so cutting 8m is the better choice.</t>
+  </si>
+  <si>
+    <t>678m 2344p 233567s</t>
+  </si>
+  <si>
+    <t>2s42 8s33 4p29 3s23 3p8</t>
+  </si>
+  <si>
+    <t>Fixing the 3s as head is best for both tile acceptance and value. The best form for the tenpai can be Mentanpin Iipeikou. Depending on how you view it, you can see both 2s and 5s as floating. There's no point in keeping both, as they're on the same suji.</t>
+  </si>
+  <si>
+    <t>789m 1123p 233567s</t>
+  </si>
+  <si>
+    <t>2s34 1p29 8s25 3s23 3p8</t>
+  </si>
+  <si>
+    <t>*1123p* edge aryanmen will be sequence + head on drawing 14p, or will be Iipeikou on drawing 23p (either kanchan or penchan wait). Both outcomes have the same probability to happen. If you end up with a bad wait Iipeikou, the win rate is going to decrease, so the aim is to avoid the bad shape tenpai by cutting 1p.</t>
+  </si>
+  <si>
+    <t>789m 1123p 235677s</t>
+  </si>
+  <si>
+    <t>1p29 7s23 2s22 3s16 8s16 3p15</t>
+  </si>
+  <si>
+    <t>If you cut 2s, you'll have a ryanmen + kanchan waiting on 4-6-9s, and the edge 1123p aryanmen. Bottleneck will be the 6-tiles aryanmen wait, instead of going there, let's drop 1 and get full ryanmen over aryanmen shapes. (TL Note: Headless shape, pretty good when you have connected tiles)</t>
+  </si>
+  <si>
+    <t>678889m 40579p 33s</t>
+  </si>
+  <si>
+    <t>678889m 40579p 11z</t>
+  </si>
+  <si>
+    <t>112m 223677888p 0s</t>
+  </si>
+  <si>
+    <t>33m 223677888p 40s</t>
+  </si>
+  <si>
+    <t>Take out the completed shape 567p. You can see the sanmenchan with a 7p attached. Fixing the head in souzu is great both for value and acceptance. See: [[67m 345677p 334s]] + [[567p]]</t>
+  </si>
+  <si>
+    <t>223067m 557p 2345s</t>
+  </si>
+  <si>
+    <t>While this can be hard at a first look, try to isolate 567p: [[223057p 23456s]] + [[567p]]. It the same shape as previous question, just replacing manzu with pinzu. It is easily solved if you take out the completed shapes.</t>
+  </si>
+  <si>
+    <t>Don't cut the 1p to aim for Tanyao. Because you have 3 heads, you should cut one of them. This way you can increase your tile acceptance. It is easy to visualize the 3 heads if you think as following: [[556m 133p 22s]] + [[345678p]]</t>
+  </si>
+  <si>
+    <t>3p19 3s18 1p13 4p13 4s12</t>
+  </si>
+  <si>
+    <t>2s22 3p19 2p17 3s16 5p13</t>
+  </si>
+  <si>
+    <t>344067m 3456p 406s</t>
   </si>
 </sst>
 </file>
@@ -878,13 +989,13 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>13</v>
@@ -896,16 +1007,16 @@
         <v>6</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L5" s="3">
         <v>1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
@@ -914,19 +1025,19 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="D6" s="3">
         <v>5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>13</v>
@@ -938,16 +1049,16 @@
         <v>6</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L6" s="3">
         <v>1</v>
       </c>
       <c r="M6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
@@ -956,19 +1067,19 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="D7" s="3">
         <v>6</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>13</v>
@@ -980,16 +1091,16 @@
         <v>6</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L7" s="3">
         <v>1</v>
       </c>
       <c r="M7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
@@ -998,19 +1109,19 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="D8" s="3">
         <v>7</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>28</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>13</v>
@@ -1022,16 +1133,16 @@
         <v>7</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L8" s="3">
         <v>1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>52</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -1040,19 +1151,19 @@
         <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="D9" s="3">
         <v>8</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>13</v>
@@ -1064,16 +1175,16 @@
         <v>7</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L9" s="3">
         <v>1</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -1082,19 +1193,19 @@
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3">
         <v>9</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>47</v>
+        <v>117</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>13</v>
@@ -1106,16 +1217,16 @@
         <v>6</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L10" s="3">
         <v>2</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -1124,19 +1235,19 @@
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="D11" s="3">
         <v>10</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>13</v>
@@ -1148,16 +1259,16 @@
         <v>4</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="L11" s="3">
         <v>1</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
@@ -1166,19 +1277,19 @@
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="D12" s="3">
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>13</v>
@@ -1190,16 +1301,16 @@
         <v>4</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="L12" s="3">
         <v>1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>71</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
@@ -1208,13 +1319,13 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="D13" s="3">
         <v>12</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>11</v>
@@ -1232,16 +1343,16 @@
         <v>7</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="L13" s="3">
         <v>1</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
@@ -1250,19 +1361,19 @@
         <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="D14" s="3">
         <v>13</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>13</v>
@@ -1280,10 +1391,10 @@
         <v>1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
@@ -1292,19 +1403,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="D15" s="3">
         <v>14</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>13</v>
@@ -1316,16 +1427,16 @@
         <v>7</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="L15" s="3">
         <v>1</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
@@ -1334,19 +1445,19 @@
         <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="D16" s="3">
         <v>15</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>13</v>
@@ -1358,136 +1469,649 @@
         <v>7</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L16" s="3">
         <v>1</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="str">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B17" s="3">
         <f t="shared" si="0"/>
-        <v/>
+        <v>16</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D17" s="3">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="str">
+      <c r="E17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="3">
+        <v>5</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L17" s="3">
+        <v>1</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B18" s="3">
         <f t="shared" si="0"/>
-        <v/>
+        <v>17</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D18" s="3">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="str">
+      <c r="E18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J18" s="3">
+        <v>5</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L18" s="3">
+        <v>1</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B19" s="3">
         <f t="shared" si="0"/>
-        <v/>
+        <v>18</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D19" s="3">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="str">
+      <c r="E19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" s="3">
+        <v>5</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L19" s="3">
+        <v>1</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B20" s="3">
         <f t="shared" si="0"/>
-        <v/>
+        <v>19</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D20" s="3">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="str">
+      <c r="E20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J20" s="3">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L20" s="3">
+        <v>1</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B21" s="3">
         <f t="shared" si="0"/>
-        <v/>
+        <v>20</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D21" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="str">
+      <c r="E21" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J21" s="3">
+        <v>7</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L21" s="3">
+        <v>1</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B22" s="3">
         <f t="shared" si="0"/>
-        <v/>
+        <v>21</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D22" s="3">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="str">
+      <c r="E22" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J22" s="3">
+        <v>7</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L22" s="3">
+        <v>1</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B23" s="3">
         <f t="shared" si="0"/>
-        <v/>
+        <v>22</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D23" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="str">
+      <c r="E23" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J23" s="3">
+        <v>7</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="L23" s="3">
+        <v>1</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B24" s="3">
         <f t="shared" si="0"/>
-        <v/>
+        <v>23</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D24" s="3">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="str">
+      <c r="E24" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="3">
+        <v>7</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L24" s="3">
+        <v>1</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B25" s="3">
         <f t="shared" si="0"/>
-        <v/>
+        <v>24</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D25" s="3">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="str">
+      <c r="E25" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J25" s="3">
+        <v>7</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L25" s="3">
+        <v>1</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B26" s="3">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="str">
+        <v>25</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="3">
+        <v>25</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J26" s="3">
+        <v>7</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L26" s="3">
+        <v>1</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B27" s="3">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="str">
+        <v>26</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="3">
+        <v>26</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J27" s="3">
+        <v>7</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L27" s="3">
+        <v>1</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B28" s="3">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B29" s="3" t="str">
+        <v>27</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="3">
+        <v>27</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J28" s="3">
+        <v>7</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="L28" s="3">
+        <v>1</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B29" s="3">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="3" t="str">
+        <v>28</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="3">
+        <v>28</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J29" s="3">
+        <v>7</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L29" s="3">
+        <v>1</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B30" s="3">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B31" s="3" t="str">
+        <v>29</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="3">
+        <v>29</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J30" s="3">
+        <v>7</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L30" s="3">
+        <v>1</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B31" s="3">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="3">
+        <v>30</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J31" s="3">
+        <v>7</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L31" s="3">
+        <v>1</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -28677,5 +29301,6 @@
   <autoFilter ref="B1:N1" xr:uid="{2AF11863-DCFD-4B14-8C82-ADD0D5B6E1FA}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>